--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UE SANT CUGAT - OCCIDENT.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UE SANT CUGAT - OCCIDENT.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>91.26530000000001</v>
+        <v>77.42370000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>87.51349999999999</v>
+        <v>81.5222</v>
       </c>
       <c r="F2" t="n">
-        <v>3.751600000000001</v>
+        <v>-4.098499999999999</v>
       </c>
       <c r="G2" t="n">
         <v>52.5624</v>
@@ -610,13 +610,13 @@
         <v>62.8877</v>
       </c>
       <c r="S2" t="n">
-        <v>26.2151</v>
+        <v>12.3732</v>
       </c>
       <c r="T2" t="n">
-        <v>12.0878</v>
+        <v>6.0964</v>
       </c>
       <c r="U2" t="n">
-        <v>14.127</v>
+        <v>6.276599999999999</v>
       </c>
       <c r="V2" t="n">
         <v>25.1845</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>M. GONZALEZ DE UBIETA BELLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>18.3493</v>
+        <v>27.5582</v>
       </c>
       <c r="E3" t="n">
-        <v>22.9207</v>
+        <v>17.0152</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.5717</v>
+        <v>10.543</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9847999999999995</v>
+        <v>-0.1276000000000002</v>
       </c>
       <c r="H3" t="n">
-        <v>5.561</v>
+        <v>-0.2365</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.5762</v>
+        <v>0.1088000000000003</v>
       </c>
       <c r="J3" t="n">
-        <v>17.324</v>
+        <v>33.1118</v>
       </c>
       <c r="K3" t="n">
-        <v>13.2279</v>
+        <v>14.8546</v>
       </c>
       <c r="L3" t="n">
-        <v>4.0966</v>
+        <v>18.2569</v>
       </c>
       <c r="M3" t="n">
-        <v>-16.3394</v>
+        <v>-33.2391</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.666700000000001</v>
+        <v>-15.091</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.672800000000001</v>
+        <v>-18.1483</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3968000000000004</v>
+        <v>10.316</v>
       </c>
       <c r="Q3" t="n">
-        <v>-27.9719</v>
+        <v>-48.8023</v>
       </c>
       <c r="R3" t="n">
-        <v>27.5755</v>
+        <v>59.1184</v>
       </c>
       <c r="S3" t="n">
-        <v>25.4245</v>
+        <v>0.7027999999999996</v>
       </c>
       <c r="T3" t="n">
-        <v>23.6891</v>
+        <v>3.1148</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7352</v>
+        <v>-2.4118</v>
       </c>
       <c r="V3" t="n">
-        <v>-7.6636</v>
+        <v>16.6672</v>
       </c>
       <c r="W3" t="n">
-        <v>9.8796</v>
+        <v>29.5916</v>
       </c>
       <c r="X3" t="n">
-        <v>-17.5431</v>
+        <v>-12.9241</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. GONZALEZ DE UBIETA BELLO</t>
+          <t>D. GUILLEN VIVES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>14.1159</v>
+        <v>9.343500000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>7.929200000000001</v>
+        <v>1.8975</v>
       </c>
       <c r="F4" t="n">
-        <v>6.186800000000001</v>
+        <v>7.446</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1276000000000002</v>
+        <v>11.239</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2365</v>
+        <v>0.1837000000000002</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1088000000000003</v>
+        <v>11.0553</v>
       </c>
       <c r="J4" t="n">
-        <v>33.1118</v>
+        <v>10.3125</v>
       </c>
       <c r="K4" t="n">
-        <v>14.8546</v>
+        <v>2.5096</v>
       </c>
       <c r="L4" t="n">
-        <v>18.2569</v>
+        <v>7.8029</v>
       </c>
       <c r="M4" t="n">
-        <v>-33.2391</v>
+        <v>0.9265999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-15.091</v>
+        <v>-2.3259</v>
       </c>
       <c r="O4" t="n">
-        <v>-18.1483</v>
+        <v>3.2524</v>
       </c>
       <c r="P4" t="n">
-        <v>10.316</v>
+        <v>0.5951000000000002</v>
       </c>
       <c r="Q4" t="n">
-        <v>-48.8023</v>
+        <v>-17.4576</v>
       </c>
       <c r="R4" t="n">
-        <v>59.1184</v>
+        <v>18.053</v>
       </c>
       <c r="S4" t="n">
-        <v>-12.7397</v>
+        <v>-1.8561</v>
       </c>
       <c r="T4" t="n">
-        <v>-5.9716</v>
+        <v>0.1372000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-6.7683</v>
+        <v>-1.9933</v>
       </c>
       <c r="V4" t="n">
-        <v>16.6672</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>29.5916</v>
+        <v>8.905999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>-12.9241</v>
+        <v>-9.5406</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. GUILLEN VIVES</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>2.136399999999999</v>
+        <v>3.3541</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6961</v>
+        <v>7.7355</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8325</v>
+        <v>-4.381</v>
       </c>
       <c r="G5" t="n">
-        <v>11.239</v>
+        <v>0.9847999999999995</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1837000000000002</v>
+        <v>5.561</v>
       </c>
       <c r="I5" t="n">
-        <v>11.0553</v>
+        <v>-4.5762</v>
       </c>
       <c r="J5" t="n">
-        <v>10.3125</v>
+        <v>17.324</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5096</v>
+        <v>13.2279</v>
       </c>
       <c r="L5" t="n">
-        <v>7.8029</v>
+        <v>4.0966</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9265999999999999</v>
+        <v>-16.3394</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.3259</v>
+        <v>-7.666700000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2524</v>
+        <v>-8.672800000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5951000000000002</v>
+        <v>-0.3968000000000004</v>
       </c>
       <c r="Q5" t="n">
-        <v>-17.4576</v>
+        <v>-27.9719</v>
       </c>
       <c r="R5" t="n">
-        <v>18.053</v>
+        <v>27.5755</v>
       </c>
       <c r="S5" t="n">
-        <v>-9.0632</v>
+        <v>10.4295</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.4567</v>
+        <v>8.5038</v>
       </c>
       <c r="U5" t="n">
-        <v>-5.6064</v>
+        <v>1.9254</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-7.6636</v>
       </c>
       <c r="W5" t="n">
-        <v>8.905999999999999</v>
+        <v>9.8796</v>
       </c>
       <c r="X5" t="n">
-        <v>-9.5406</v>
+        <v>-17.5431</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. HAGENAERS COS</t>
+          <t>W. MCDONALD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002799999999999692</v>
+        <v>-3.2165</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5361</v>
+        <v>-4.5454</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5387</v>
+        <v>1.3289</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6715999999999991</v>
+        <v>-1.5166</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6943</v>
+        <v>1.7484</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.0229</v>
+        <v>-3.2649</v>
       </c>
       <c r="J6" t="n">
-        <v>14.4016</v>
+        <v>0.1890000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>11.9162</v>
+        <v>1.7699</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4857</v>
+        <v>-1.581</v>
       </c>
       <c r="M6" t="n">
-        <v>-13.73</v>
+        <v>-1.7056</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.2215</v>
+        <v>-0.02160000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-6.508500000000001</v>
+        <v>-1.684</v>
       </c>
       <c r="P6" t="n">
-        <v>6.7453</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q6" t="n">
-        <v>-38.0895</v>
+        <v>-5.951499999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>44.8349</v>
+        <v>3.7693</v>
       </c>
       <c r="S6" t="n">
-        <v>17.5273</v>
+        <v>-0.3869</v>
       </c>
       <c r="T6" t="n">
-        <v>18.8889</v>
+        <v>-0.5213</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3617</v>
+        <v>0.1344</v>
       </c>
       <c r="V6" t="n">
-        <v>-24.9413</v>
+        <v>0.8692</v>
       </c>
       <c r="W6" t="n">
-        <v>3.2631</v>
+        <v>1.7384</v>
       </c>
       <c r="X6" t="n">
-        <v>-28.2042</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. MCDONALD</t>
+          <t>D. IRUELA RUBIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.763100000000001</v>
+        <v>-4.1433</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.871700000000001</v>
+        <v>-2.438</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1087</v>
+        <v>-1.7054</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5166</v>
+        <v>-2.7685</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7484</v>
+        <v>-17.1466</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.2649</v>
+        <v>14.3783</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1890000000000001</v>
+        <v>15.8999</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7699</v>
+        <v>-6.1082</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.581</v>
+        <v>22.0078</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7056</v>
+        <v>-18.6684</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.02160000000000001</v>
+        <v>-11.0386</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.684</v>
+        <v>-7.6297</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.1822</v>
+        <v>0.3966999999999998</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.951499999999999</v>
+        <v>-26.3849</v>
       </c>
       <c r="R7" t="n">
-        <v>3.7693</v>
+        <v>26.7819</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9334</v>
+        <v>-2.6483</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.8476</v>
+        <v>-2.6681</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.08579999999999999</v>
+        <v>0.01990000000000008</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8692</v>
+        <v>0.8769000000000005</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7384</v>
+        <v>10.7157</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8692</v>
+        <v>-9.838699999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.6592</v>
+        <v>-7.112000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-8.1785</v>
+        <v>-6.9653</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4808999999999997</v>
+        <v>-0.1464999999999997</v>
       </c>
       <c r="G8" t="n">
         <v>-7.0795</v>
@@ -1078,13 +1078,13 @@
         <v>24.2033</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.2548</v>
+        <v>-1.7073</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3254</v>
+        <v>-0.1126</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.9291</v>
+        <v>-1.595</v>
       </c>
       <c r="V8" t="n">
         <v>-7.4505</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. IRUELA RUBIO</t>
+          <t>J. HAGENAERS COS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>-13.0414</v>
+        <v>-11.0967</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.602399999999999</v>
+        <v>-12.5441</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.439</v>
+        <v>1.447299999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.7685</v>
+        <v>0.6715999999999991</v>
       </c>
       <c r="H9" t="n">
-        <v>-17.1466</v>
+        <v>4.6943</v>
       </c>
       <c r="I9" t="n">
-        <v>14.3783</v>
+        <v>-4.0229</v>
       </c>
       <c r="J9" t="n">
-        <v>15.8999</v>
+        <v>14.4016</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.1082</v>
+        <v>11.9162</v>
       </c>
       <c r="L9" t="n">
-        <v>22.0078</v>
+        <v>2.4857</v>
       </c>
       <c r="M9" t="n">
-        <v>-18.6684</v>
+        <v>-13.73</v>
       </c>
       <c r="N9" t="n">
-        <v>-11.0386</v>
+        <v>-7.2215</v>
       </c>
       <c r="O9" t="n">
-        <v>-7.6297</v>
+        <v>-6.508500000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3966999999999998</v>
+        <v>6.7453</v>
       </c>
       <c r="Q9" t="n">
-        <v>-26.3849</v>
+        <v>-38.0895</v>
       </c>
       <c r="R9" t="n">
-        <v>26.7819</v>
+        <v>44.8349</v>
       </c>
       <c r="S9" t="n">
-        <v>-11.5465</v>
+        <v>6.4278</v>
       </c>
       <c r="T9" t="n">
-        <v>-9.832800000000001</v>
+        <v>7.881</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.7139</v>
+        <v>-1.4534</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8769000000000005</v>
+        <v>-24.9413</v>
       </c>
       <c r="W9" t="n">
-        <v>10.7157</v>
+        <v>3.2631</v>
       </c>
       <c r="X9" t="n">
-        <v>-9.838699999999999</v>
+        <v>-28.2042</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. FEIXA MORANCHO</t>
+          <t>F. LOPEZ BARCELO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-13.298</v>
+        <v>-11.8266</v>
       </c>
       <c r="E10" t="n">
-        <v>11.1588</v>
+        <v>-4.6876</v>
       </c>
       <c r="F10" t="n">
-        <v>-24.4568</v>
+        <v>-7.1391</v>
       </c>
       <c r="G10" t="n">
-        <v>7.2647</v>
+        <v>-9.0991</v>
       </c>
       <c r="H10" t="n">
-        <v>12.5538</v>
+        <v>-2.1416</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.2888</v>
+        <v>-6.9574</v>
       </c>
       <c r="J10" t="n">
-        <v>25.1331</v>
+        <v>-1.881</v>
       </c>
       <c r="K10" t="n">
-        <v>21.3479</v>
+        <v>0.9698</v>
       </c>
       <c r="L10" t="n">
-        <v>3.7854</v>
+        <v>-2.8509</v>
       </c>
       <c r="M10" t="n">
-        <v>-17.8684</v>
+        <v>-7.2181</v>
       </c>
       <c r="N10" t="n">
-        <v>-8.7942</v>
+        <v>-3.1113</v>
       </c>
       <c r="O10" t="n">
-        <v>-9.0741</v>
+        <v>-4.1066</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7856</v>
+        <v>0.3967000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-23.2106</v>
+        <v>-5.1579</v>
       </c>
       <c r="R10" t="n">
-        <v>24.9964</v>
+        <v>5.5549</v>
       </c>
       <c r="S10" t="n">
-        <v>9.263599999999999</v>
+        <v>0.7609999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>10.1249</v>
+        <v>1.5533</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8616</v>
+        <v>-0.7922</v>
       </c>
       <c r="V10" t="n">
-        <v>-31.6117</v>
+        <v>-3.8854</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.8884</v>
+        <v>0.7978999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-30.7234</v>
+        <v>-4.6834</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. LOPEZ BARCELO</t>
+          <t>A. NEALE GIMENEZ-CASSINA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>-15.1806</v>
+        <v>-11.8578</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.9323</v>
+        <v>-13.4362</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.2484</v>
+        <v>1.578000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-9.0991</v>
+        <v>5.087200000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1416</v>
+        <v>2.7305</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.9574</v>
+        <v>2.356599999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.881</v>
+        <v>15.74</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9698</v>
+        <v>9.582100000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.8509</v>
+        <v>6.1581</v>
       </c>
       <c r="M11" t="n">
-        <v>-7.2181</v>
+        <v>-10.653</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.1113</v>
+        <v>-6.851599999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.1066</v>
+        <v>-3.8015</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3967000000000001</v>
+        <v>-9.5221</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.1579</v>
+        <v>-30.3526</v>
       </c>
       <c r="R11" t="n">
-        <v>5.5549</v>
+        <v>20.8305</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.593</v>
+        <v>-1.8206</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6912999999999999</v>
+        <v>-2.3003</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.9018</v>
+        <v>0.4794999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.8854</v>
+        <v>-5.6019</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7978999999999999</v>
+        <v>3.477</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.6834</v>
+        <v>-9.078799999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. NEALE GIMENEZ-CASSINA</t>
+          <t>S. CASAÚ PUEYO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.7678</v>
+        <v>-20.3833</v>
       </c>
       <c r="E12" t="n">
-        <v>-18.5887</v>
+        <v>-21.4107</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1796</v>
+        <v>1.0276</v>
       </c>
       <c r="G12" t="n">
-        <v>5.087200000000001</v>
+        <v>-1.652</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7305</v>
+        <v>-11.5496</v>
       </c>
       <c r="I12" t="n">
-        <v>2.356599999999999</v>
+        <v>9.897400000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>15.74</v>
+        <v>16.9212</v>
       </c>
       <c r="K12" t="n">
-        <v>9.582100000000001</v>
+        <v>-1.9722</v>
       </c>
       <c r="L12" t="n">
-        <v>6.1581</v>
+        <v>18.8932</v>
       </c>
       <c r="M12" t="n">
-        <v>-10.653</v>
+        <v>-18.5734</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.851599999999999</v>
+        <v>-9.577400000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.8015</v>
+        <v>-8.9956</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.5221</v>
+        <v>-6.7452</v>
       </c>
       <c r="Q12" t="n">
-        <v>-30.3526</v>
+        <v>-54.7537</v>
       </c>
       <c r="R12" t="n">
-        <v>20.8305</v>
+        <v>48.0091</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.730600000000001</v>
+        <v>-2.0758</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.4526</v>
+        <v>1.3795</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2779</v>
+        <v>-3.4556</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.6019</v>
+        <v>-9.91</v>
       </c>
       <c r="W12" t="n">
-        <v>3.477</v>
+        <v>15.0424</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.078799999999999</v>
+        <v>-24.9527</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. CASAÚ PUEYO</t>
+          <t>P. FEIXA MORANCHO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-29.39</v>
+        <v>-21.4154</v>
       </c>
       <c r="E13" t="n">
-        <v>-24.341</v>
+        <v>3.8977</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.048699999999999</v>
+        <v>-25.313</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.652</v>
+        <v>7.2647</v>
       </c>
       <c r="H13" t="n">
-        <v>-11.5496</v>
+        <v>12.5538</v>
       </c>
       <c r="I13" t="n">
-        <v>9.897400000000001</v>
+        <v>-5.2888</v>
       </c>
       <c r="J13" t="n">
-        <v>16.9212</v>
+        <v>25.1331</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.9722</v>
+        <v>21.3479</v>
       </c>
       <c r="L13" t="n">
-        <v>18.8932</v>
+        <v>3.7854</v>
       </c>
       <c r="M13" t="n">
-        <v>-18.5734</v>
+        <v>-17.8684</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.577400000000001</v>
+        <v>-8.7942</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.9956</v>
+        <v>-9.0741</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.7452</v>
+        <v>1.7856</v>
       </c>
       <c r="Q13" t="n">
-        <v>-54.7537</v>
+        <v>-23.2106</v>
       </c>
       <c r="R13" t="n">
-        <v>48.0091</v>
+        <v>24.9964</v>
       </c>
       <c r="S13" t="n">
-        <v>-11.0824</v>
+        <v>1.1465</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5506</v>
+        <v>2.8637</v>
       </c>
       <c r="U13" t="n">
-        <v>-9.532</v>
+        <v>-1.7178</v>
       </c>
       <c r="V13" t="n">
-        <v>-9.91</v>
+        <v>-31.6117</v>
       </c>
       <c r="W13" t="n">
-        <v>15.0424</v>
+        <v>-0.8884</v>
       </c>
       <c r="X13" t="n">
-        <v>-24.9527</v>
+        <v>-30.7234</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-41.2387</v>
+        <v>-24.8584</v>
       </c>
       <c r="E14" t="n">
-        <v>-23.5557</v>
+        <v>-12.7634</v>
       </c>
       <c r="F14" t="n">
-        <v>-17.683</v>
+        <v>-12.0945</v>
       </c>
       <c r="G14" t="n">
         <v>-7.2761</v>
@@ -1546,13 +1546,13 @@
         <v>42.2556</v>
       </c>
       <c r="S14" t="n">
-        <v>-21.0836</v>
+        <v>-4.7032</v>
       </c>
       <c r="T14" t="n">
-        <v>-11.0512</v>
+        <v>-0.259</v>
       </c>
       <c r="U14" t="n">
-        <v>-10.0331</v>
+        <v>-4.4446</v>
       </c>
       <c r="V14" t="n">
         <v>-1.174299999999999</v>
@@ -1579,13 +1579,13 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>-51.8958</v>
+        <v>-43.673</v>
       </c>
       <c r="E15" t="n">
-        <v>-39.5687</v>
+        <v>-34.2743</v>
       </c>
       <c r="F15" t="n">
-        <v>-12.3277</v>
+        <v>-9.3988</v>
       </c>
       <c r="G15" t="n">
         <v>-26.6658</v>
@@ -1624,13 +1624,13 @@
         <v>24.0046</v>
       </c>
       <c r="S15" t="n">
-        <v>-13.5326</v>
+        <v>-5.3095</v>
       </c>
       <c r="T15" t="n">
-        <v>-5.0945</v>
+        <v>0.1995</v>
       </c>
       <c r="U15" t="n">
-        <v>-8.437900000000001</v>
+        <v>-5.5092</v>
       </c>
       <c r="V15" t="n">
         <v>-9.118600000000001</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-70.36490000000001</v>
+        <v>-41.90349999999998</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.34900000000001</v>
+        <v>-0.9969000000000108</v>
       </c>
       <c r="F16" t="n">
-        <v>-60.0175</v>
+        <v>-40.906</v>
       </c>
       <c r="G16" t="n">
         <v>21.62450000000001</v>
@@ -1672,7 +1672,7 @@
         <v>17.1804</v>
       </c>
       <c r="I16" t="n">
-        <v>4.443700000000003</v>
+        <v>4.443699999999996</v>
       </c>
       <c r="J16" t="n">
         <v>245.9295</v>
@@ -1702,13 +1702,13 @@
         <v>432.8750999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>-17.12930000000001</v>
+        <v>11.3331</v>
       </c>
       <c r="T16" t="n">
-        <v>16.51639999999999</v>
+        <v>25.8679</v>
       </c>
       <c r="U16" t="n">
-        <v>-33.6473</v>
+        <v>-14.5371</v>
       </c>
       <c r="V16" t="n">
         <v>-58.39409999999999</v>
